--- a/data/phoneme_onset_C/St09_C.xlsx
+++ b/data/phoneme_onset_C/St09_C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/IMT/TESI/linguistic_pipeline_EEG/data/phoneme_onset_C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{4652040C-4E9A-4B1F-B8D8-91B0F9DD62A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="6_{4652040C-4E9A-4B1F-B8D8-91B0F9DD62A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EADF17E-D4A9-4740-BE47-B8B693CE34AC}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13959,6 +13959,9 @@
       <c r="A595">
         <v>2909444</v>
       </c>
+      <c r="C595">
+        <v>132</v>
+      </c>
       <c r="D595" t="s">
         <v>26</v>
       </c>
@@ -17076,7 +17079,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A753">
         <v>3655008</v>
       </c>
@@ -17096,7 +17099,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A754">
         <v>3659859</v>
       </c>
@@ -17116,7 +17119,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A755">
         <v>3664269</v>
       </c>
@@ -17136,7 +17139,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A756">
         <v>3668679</v>
       </c>
@@ -17156,7 +17159,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A757">
         <v>3670443</v>
       </c>
@@ -17176,7 +17179,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A758">
         <v>3673971</v>
       </c>
@@ -17196,7 +17199,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A759">
         <v>3676176</v>
       </c>
@@ -17216,7 +17219,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A760">
         <v>3678381</v>
       </c>
@@ -17235,8 +17238,12 @@
       <c r="G760" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="K760">
+        <f>COUNTIF(A1:A1859, "")</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="761" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A761">
         <v>3681909</v>
       </c>
@@ -17256,7 +17263,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A762">
         <v>3687642</v>
       </c>
@@ -17276,7 +17283,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A763">
         <v>3697344</v>
       </c>
@@ -17296,7 +17303,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A764">
         <v>3699549</v>
       </c>
@@ -17316,7 +17323,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A765">
         <v>3717189</v>
       </c>
@@ -17336,7 +17343,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A766">
         <v>3720276</v>
       </c>
@@ -17356,7 +17363,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A767">
         <v>3722040</v>
       </c>
@@ -17376,7 +17383,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A768">
         <v>3728214</v>
       </c>
